--- a/evals/unit_tests_comparative/test05_gemm_identical_runtime_roofline/analysis_output_ref/perf_report_trace2.xlsx
+++ b/evals/unit_tests_comparative/test05_gemm_identical_runtime_roofline/analysis_output_ref/perf_report_trace2.xlsx
@@ -11,8 +11,9 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="unified_perf_callstacks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GEMM" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,421 +972,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>process_name</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>process_label</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>thread_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Input Dims</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Input type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Input Strides</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ex_UID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>operation_count</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>total_duration_us</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>mean_duration_us</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>std_duration_us</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>GFLOPS</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Data Moved (MB)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>FLOPS/Byte</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Compute Spec</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Roofline Bound</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_mean</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_std</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_mean</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_std</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_mean</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_std</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_median</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_min</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_max</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_median</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_min</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_max</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_median</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_min</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_max</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Roofline Time (µs)_first</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_mean</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_median</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_std</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_min</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_max</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_median</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_min</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_max</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>kernel_details_summary</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>trunc_kernel_details</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>perf_params</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>has_perf_model</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Cumulative Percentage (%)</t>
+          <t>call_stack</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>aten::mm</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>GEMM</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>((512, 512), (512, 512))</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>('c10::bfloat16', 'c10::bfloat16')</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M2" t="n">
-        <v>15</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>0.268435456</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>170.6666666666667</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>matrix_bf16</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>COMPUTE_BOUND</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>0.007864319999999999</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>1.34217728</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>200</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.007864319999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.007864319999999999</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.007864319999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.34217728</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.34217728</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.34217728</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.3791461242937853</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.1895730621468927</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.1895730621468927</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>0.1895730621468927</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.1895730621468927</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel', 'stream': 7, 'gpu_op_uid': 6, 'count': 1, 'total_duration_us': np.float64(200.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(200.0), 'median_duration_us': np.float64(200.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(200.0), 'max_duration_us': np.float64(200.0)}]</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(200.0)}]</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>{'M': 512, 'N': 512, 'K': 512, 'bias': False, 'stride_A': None, 'stride_B': None, 'dtype_A_B': ('c10::bfloat16', 'c10::bfloat16'), 'B': 1}</t>
-        </is>
-      </c>
-      <c r="AV2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>100</v>
+          <t>aten::mm =&gt; aten::mm</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1399,6 +1028,444 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>op category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>process_label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Input type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ex_UID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>operation_count</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>total_duration_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mean_duration_us</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>std_duration_us</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Roofline Bound</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_median</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_min</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_max</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Roofline Time (µs)_first</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_mean</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_median</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_std</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_min</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_max</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details_summary</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>perf_params</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>has_perf_model</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_call_stack</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative Percentage (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::mm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>((512, 512), (512, 512))</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>('c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0.268435456</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>170.6666666666667</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>COMPUTE_BOUND</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0.007864319999999999</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>1.34217728</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.007864319999999999</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.007864319999999999</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.007864319999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.34217728</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.34217728</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.34217728</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3791461242937853</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1895730621468927</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1895730621468927</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>0.1895730621468927</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.1895730621468927</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(200.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(200.0), 'median_duration_us': np.float64(200.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(200.0), 'max_duration_us': np.float64(200.0)}]</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warp...', 'stream': 7, 'mean_duration_us': np.float64(200.0)}]</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>{'M': 512, 'N': 512, 'K': 512, 'bias': False, 'stride_A': None, 'stride_B': None, 'dtype_A_B': ('c10::bfloat16', 'c10::bfloat16'), 'B': 1}</t>
+        </is>
+      </c>
+      <c r="AV2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>aten::mm =&gt; aten::mm</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AV2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1773,7 +1840,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel', 'stream': 7, 'gpu_op_uid': 6, 'count': 1, 'total_duration_us': np.float64(200.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(200.0), 'median_duration_us': np.float64(200.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(200.0), 'max_duration_us': np.float64(200.0)}]</t>
+          <t>[{'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize256x128x64_warpgroupsize2x1x1_execute_segment_k_off_kernel', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(200.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(200.0), 'median_duration_us': np.float64(200.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(200.0), 'max_duration_us': np.float64(200.0)}]</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
